--- a/users.xlsx
+++ b/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kagan\Project\Entrepreneurship\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kagan\Project\Certification Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588BFF72-7CF8-4089-BE52-4C0000D10C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801BB183-823A-43AE-86D1-633EE2F4FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -28,10 +28,22 @@
     <t>Email</t>
   </si>
   <si>
-    <t>kaganeshwar414@gmail.com</t>
-  </si>
-  <si>
-    <t>Kagan</t>
+    <t>Reetha M</t>
+  </si>
+  <si>
+    <t>mreetha2005@gmail.com</t>
+  </si>
+  <si>
+    <t>Abi P</t>
+  </si>
+  <si>
+    <t>abip8176@gmail.com</t>
+  </si>
+  <si>
+    <t>Thara R</t>
+  </si>
+  <si>
+    <t>thara142005@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -55,23 +67,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -94,20 +115,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -410,10 +501,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -423,24 +518,170 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
-    </row>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{5AFB5D51-6D87-46BF-9E33-3CF4F1E2C3F8}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>